--- a/dev/StructureDefinition-ph-core-location.xlsx
+++ b/dev/StructureDefinition-ph-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T05:11:07+00:00</t>
+    <t>2026-03-16T07:24:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-location.xlsx
+++ b/dev/StructureDefinition-ph-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T07:24:26+00:00</t>
+    <t>2026-03-16T20:48:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-location.xlsx
+++ b/dev/StructureDefinition-ph-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T20:48:05+00:00</t>
+    <t>2026-03-16T20:59:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-location.xlsx
+++ b/dev/StructureDefinition-ph-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T20:59:47+00:00</t>
+    <t>2026-03-16T21:16:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-location.xlsx
+++ b/dev/StructureDefinition-ph-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T21:16:15+00:00</t>
+    <t>2026-03-16T21:44:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-location.xlsx
+++ b/dev/StructureDefinition-ph-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T21:44:19+00:00</t>
+    <t>2026-03-16T21:58:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-location.xlsx
+++ b/dev/StructureDefinition-ph-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T21:58:37+00:00</t>
+    <t>2026-03-16T22:06:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-location.xlsx
+++ b/dev/StructureDefinition-ph-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T22:06:54+00:00</t>
+    <t>2026-03-16T22:26:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-location.xlsx
+++ b/dev/StructureDefinition-ph-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T22:26:22+00:00</t>
+    <t>2026-03-19T20:53:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-location.xlsx
+++ b/dev/StructureDefinition-ph-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T20:53:49+00:00</t>
+    <t>2026-03-19T21:27:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-location.xlsx
+++ b/dev/StructureDefinition-ph-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T21:27:42+00:00</t>
+    <t>2026-04-08T04:20:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-location.xlsx
+++ b/dev/StructureDefinition-ph-core-location.xlsx
@@ -9,11 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$48</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1392" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1666" uniqueCount="311">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T04:20:57+00:00</t>
+    <t>2026-04-10T05:32:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -617,6 +620,79 @@
     <t>.code</t>
   </si>
   <si>
+    <t>Location.type.id</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>Location.type.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Location.type.coding</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Location.type.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
     <t>Location.telecom</t>
   </si>
   <si>
@@ -636,7 +712,7 @@
     <t>Location.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {Address|http://doh.gov.ph/fhir/ph-core/StructureDefinition/ph-core-address}
+    <t xml:space="preserve">Address {http://doh.gov.ph/fhir/ph-core/StructureDefinition/ph-core-address}
 </t>
   </si>
   <si>
@@ -677,6 +753,18 @@
   </si>
   <si>
     <t>.playingEntity [classCode=PLC].code</t>
+  </si>
+  <si>
+    <t>Location.physicalType.id</t>
+  </si>
+  <si>
+    <t>Location.physicalType.extension</t>
+  </si>
+  <si>
+    <t>Location.physicalType.coding</t>
+  </si>
+  <si>
+    <t>Location.physicalType.text</t>
   </si>
   <si>
     <t>Location.position</t>
@@ -701,22 +789,7 @@
     <t>Location.position.id</t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
     <t>Location.position.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Location.position.modifierExtension</t>
@@ -1037,6 +1110,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -1210,7 +1298,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL40"/>
+  <dimension ref="A1:AL48"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="36.84765625" customWidth="true" bestFit="true"/>
@@ -1223,7 +1311,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="68.703125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="65.87109375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1241,7 +1329,7 @@
     <col min="26" max="26" width="58.125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="32.84765625" customWidth="true" bestFit="true" hidden="true"/>
@@ -1368,7 +1456,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -1474,7 +1562,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>83</v>
       </c>
@@ -1582,7 +1670,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>91</v>
       </c>
@@ -1688,7 +1776,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>97</v>
       </c>
@@ -1796,7 +1884,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>103</v>
       </c>
@@ -1904,7 +1992,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>112</v>
       </c>
@@ -2012,7 +2100,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>120</v>
       </c>
@@ -2120,7 +2208,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>128</v>
       </c>
@@ -2228,7 +2316,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>136</v>
       </c>
@@ -2338,7 +2426,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>141</v>
       </c>
@@ -2446,7 +2534,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>148</v>
       </c>
@@ -2552,7 +2640,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
         <v>156</v>
       </c>
@@ -2658,7 +2746,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
         <v>163</v>
       </c>
@@ -2766,7 +2854,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
         <v>169</v>
       </c>
@@ -2876,7 +2964,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
         <v>174</v>
       </c>
@@ -2984,7 +3072,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
         <v>179</v>
       </c>
@@ -3113,7 +3201,7 @@
         <v>77</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>75</v>
@@ -3200,7 +3288,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
         <v>194</v>
       </c>
@@ -3216,7 +3304,7 @@
         <v>76</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>75</v>
@@ -3228,13 +3316,13 @@
         <v>75</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3285,44 +3373,44 @@
         <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" hidden="true">
+      <c r="A20" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AL19" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="2">
-        <v>199</v>
-      </c>
       <c r="B20" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>75</v>
+        <v>129</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>75</v>
@@ -3334,20 +3422,18 @@
         <v>75</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>201</v>
+        <v>131</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>204</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>75</v>
       </c>
@@ -3383,34 +3469,34 @@
         <v>75</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>75</v>
+        <v>200</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>75</v>
+        <v>201</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>75</v>
+        <v>202</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>205</v>
+        <v>162</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>75</v>
@@ -3418,10 +3504,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3432,10 +3518,10 @@
         <v>76</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>75</v>
@@ -3444,17 +3530,19 @@
         <v>85</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>188</v>
+        <v>157</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="N21" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="O21" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>75</v>
@@ -3479,13 +3567,13 @@
         <v>75</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>210</v>
+        <v>75</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>211</v>
+        <v>75</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>212</v>
+        <v>75</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>75</v>
@@ -3503,13 +3591,13 @@
         <v>75</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>75</v>
@@ -3518,18 +3606,18 @@
         <v>96</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>186</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3543,26 +3631,28 @@
         <v>84</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="O22" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="L22" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N22" s="2"/>
-      <c r="O22" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>75</v>
@@ -3611,7 +3701,7 @@
         <v>75</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -3626,18 +3716,18 @@
         <v>96</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3648,7 +3738,7 @@
         <v>76</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>75</v>
@@ -3660,13 +3750,13 @@
         <v>75</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>164</v>
+        <v>219</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3717,44 +3807,44 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK23" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="24" hidden="true">
+      <c r="A24" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="AG23" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI23" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ23" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK23" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s" s="2">
-        <v>224</v>
-      </c>
       <c r="B24" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>129</v>
+        <v>75</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>75</v>
@@ -3766,18 +3856,20 @@
         <v>75</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>131</v>
+        <v>225</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="O24" s="2"/>
+        <v>227</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>75</v>
       </c>
@@ -3825,22 +3917,22 @@
         <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>162</v>
+        <v>229</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>75</v>
@@ -3848,45 +3940,43 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>228</v>
+        <v>75</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J25" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>130</v>
+        <v>188</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>133</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>139</v>
+        <v>233</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>75</v>
@@ -3911,13 +4001,13 @@
         <v>75</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>75</v>
+        <v>234</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>75</v>
+        <v>235</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>75</v>
+        <v>236</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>75</v>
@@ -3935,33 +4025,33 @@
         <v>75</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>127</v>
+        <v>237</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="26">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3969,7 +4059,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>84</v>
@@ -3984,13 +4074,13 @@
         <v>75</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>233</v>
+        <v>164</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>234</v>
+        <v>195</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>235</v>
+        <v>196</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4041,10 +4131,10 @@
         <v>75</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>232</v>
+        <v>197</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>84</v>
@@ -4053,32 +4143,32 @@
         <v>75</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>236</v>
+        <v>162</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>75</v>
+        <v>129</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>75</v>
@@ -4090,15 +4180,17 @@
         <v>75</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>233</v>
+        <v>130</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>238</v>
+        <v>131</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>133</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>75</v>
@@ -4135,34 +4227,34 @@
         <v>75</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>75</v>
+        <v>200</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>75</v>
+        <v>201</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>75</v>
+        <v>202</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>237</v>
+        <v>203</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>236</v>
+        <v>162</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>75</v>
@@ -4184,28 +4276,32 @@
         <v>76</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>233</v>
+        <v>157</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>208</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>75</v>
       </c>
@@ -4253,13 +4349,13 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>240</v>
+        <v>209</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>75</v>
@@ -4268,7 +4364,7 @@
         <v>96</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>236</v>
+        <v>210</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>75</v>
@@ -4276,10 +4372,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4293,7 +4389,7 @@
         <v>84</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>75</v>
@@ -4302,19 +4398,19 @@
         <v>85</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>244</v>
+        <v>164</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>246</v>
+        <v>213</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>247</v>
+        <v>214</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>248</v>
+        <v>215</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>75</v>
@@ -4363,7 +4459,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>243</v>
+        <v>216</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -4378,18 +4474,18 @@
         <v>96</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>249</v>
+        <v>217</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4412,17 +4508,17 @@
         <v>75</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>75</v>
@@ -4471,7 +4567,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -4486,18 +4582,18 @@
         <v>96</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4508,7 +4604,7 @@
         <v>76</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>75</v>
@@ -4520,17 +4616,15 @@
         <v>75</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>215</v>
+        <v>164</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>257</v>
+        <v>195</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>75</v>
@@ -4579,44 +4673,44 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>256</v>
+        <v>197</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>260</v>
+        <v>162</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>75</v>
+        <v>129</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>75</v>
@@ -4628,15 +4722,17 @@
         <v>75</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>164</v>
+        <v>130</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>221</v>
+        <v>131</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>133</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>75</v>
@@ -4685,19 +4781,19 @@
         <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>223</v>
+        <v>203</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>75</v>
+        <v>135</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>162</v>
@@ -4706,16 +4802,16 @@
         <v>75</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>129</v>
+        <v>251</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -4728,24 +4824,26 @@
         <v>75</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K33" t="s" s="2">
         <v>130</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>131</v>
+        <v>252</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>225</v>
+        <v>253</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="O33" s="2"/>
+      <c r="O33" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>75</v>
       </c>
@@ -4793,7 +4891,7 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>226</v>
+        <v>254</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -4808,54 +4906,50 @@
         <v>135</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>162</v>
+        <v>127</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>228</v>
+        <v>75</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>130</v>
+        <v>256</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>229</v>
+        <v>257</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>75</v>
       </c>
@@ -4903,33 +4997,33 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>231</v>
+        <v>255</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>127</v>
+        <v>259</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4937,10 +5031,10 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>75</v>
@@ -4952,13 +5046,13 @@
         <v>75</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>104</v>
+        <v>256</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4985,13 +5079,13 @@
         <v>75</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>267</v>
+        <v>75</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>268</v>
+        <v>75</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>75</v>
@@ -5009,13 +5103,13 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>75</v>
@@ -5024,18 +5118,18 @@
         <v>96</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5058,13 +5152,13 @@
         <v>75</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>270</v>
+        <v>256</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5115,7 +5209,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -5130,18 +5224,18 @@
         <v>96</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5161,19 +5255,23 @@
         <v>75</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+        <v>269</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>271</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>75</v>
       </c>
@@ -5221,7 +5319,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5236,18 +5334,18 @@
         <v>96</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5273,13 +5371,15 @@
         <v>274</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
+      <c r="O38" t="s" s="2">
+        <v>277</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>75</v>
       </c>
@@ -5327,7 +5427,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -5342,18 +5442,18 @@
         <v>96</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5364,7 +5464,7 @@
         <v>76</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>75</v>
@@ -5376,15 +5476,17 @@
         <v>75</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>164</v>
+        <v>243</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>75</v>
@@ -5433,13 +5535,13 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>75</v>
@@ -5448,18 +5550,18 @@
         <v>96</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>162</v>
+        <v>283</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5470,7 +5572,7 @@
         <v>76</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>75</v>
@@ -5482,18 +5584,16 @@
         <v>75</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>284</v>
+        <v>164</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>285</v>
+        <v>195</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>286</v>
+        <v>196</v>
       </c>
       <c r="N40" s="2"/>
-      <c r="O40" t="s" s="2">
-        <v>287</v>
-      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>75</v>
       </c>
@@ -5541,19 +5641,19 @@
         <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>283</v>
+        <v>197</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>162</v>
@@ -5562,7 +5662,881 @@
         <v>75</v>
       </c>
     </row>
+    <row r="41" hidden="true">
+      <c r="A41" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="O41" s="2"/>
+      <c r="P41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q41" s="2"/>
+      <c r="R41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="42" hidden="true">
+      <c r="A42" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K42" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="P42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q42" s="2"/>
+      <c r="R42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="43" hidden="true">
+      <c r="A43" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
+      <c r="P43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q43" s="2"/>
+      <c r="R43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="44" hidden="true">
+      <c r="A44" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
+      <c r="P44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="45" hidden="true">
+      <c r="A45" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
+      <c r="P45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="46" hidden="true">
+      <c r="A46" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
+      <c r="P46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="47" hidden="true">
+      <c r="A47" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
+      <c r="P47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="48" hidden="true">
+      <c r="A48" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="P48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:AL48">
+    <filterColumn colId="7">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="27">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI47">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/dev/StructureDefinition-ph-core-location.xlsx
+++ b/dev/StructureDefinition-ph-core-location.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T05:32:03+00:00</t>
+    <t>2026-04-10T05:44:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-location.xlsx
+++ b/dev/StructureDefinition-ph-core-location.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$64</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1666" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2207" uniqueCount="406">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T05:44:36+00:00</t>
+    <t>2026-05-26T03:51:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -729,6 +729,303 @@
   </si>
   <si>
     <t>.addr</t>
+  </si>
+  <si>
+    <t>Location.address.id</t>
+  </si>
+  <si>
+    <t>Location.address.extension</t>
+  </si>
+  <si>
+    <t>Location.address.extension:region</t>
+  </si>
+  <si>
+    <t>region</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://doh.gov.ph/fhir/ph-core/StructureDefinition/region}
+</t>
+  </si>
+  <si>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>Region from the standard geographic code.</t>
+  </si>
+  <si>
+    <t>Location.address.extension:province</t>
+  </si>
+  <si>
+    <t>province</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://doh.gov.ph/fhir/ph-core/StructureDefinition/province}
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>Province from the standard geographic code.</t>
+  </si>
+  <si>
+    <t>Location.address.extension:cityMunicipality</t>
+  </si>
+  <si>
+    <t>cityMunicipality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://doh.gov.ph/fhir/ph-core/StructureDefinition/city-municipality}
+</t>
+  </si>
+  <si>
+    <t>City/Municipality</t>
+  </si>
+  <si>
+    <t>City/municipality from the standard geographic code.</t>
+  </si>
+  <si>
+    <t>Location.address.extension:barangay</t>
+  </si>
+  <si>
+    <t>barangay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://doh.gov.ph/fhir/ph-core/StructureDefinition/barangay}
+</t>
+  </si>
+  <si>
+    <t>Barangay from the standard geographic code.</t>
+  </si>
+  <si>
+    <t>Location.address.use</t>
+  </si>
+  <si>
+    <t>home | work | temp | old | billing - purpose of this address</t>
+  </si>
+  <si>
+    <t>The purpose of this address.</t>
+  </si>
+  <si>
+    <t>Applications can assume that an address is current unless it explicitly says that it is temporary or old.</t>
+  </si>
+  <si>
+    <t>Allows an appropriate address to be chosen from a list of many.</t>
+  </si>
+  <si>
+    <t>home</t>
+  </si>
+  <si>
+    <t>The use of an address.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/address-use|4.0.1</t>
+  </si>
+  <si>
+    <t>Address.use</t>
+  </si>
+  <si>
+    <t>unique(./use)</t>
+  </si>
+  <si>
+    <t>Location.address.type</t>
+  </si>
+  <si>
+    <t>postal | physical | both</t>
+  </si>
+  <si>
+    <t>Distinguishes between physical addresses (those you can visit) and mailing addresses (e.g. PO Boxes and care-of addresses). Most addresses are both.</t>
+  </si>
+  <si>
+    <t>The definition of Address states that "address is intended to describe postal addresses, not physical locations". However, many applications track whether an address has a dual purpose of being a location that can be visited as well as being a valid delivery destination, and Postal addresses are often used as proxies for physical locations (also see the [Location](http://hl7.org/fhir/R4/location.html#) resource).</t>
+  </si>
+  <si>
+    <t>both</t>
+  </si>
+  <si>
+    <t>The type of an address (physical / postal).</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/address-type|4.0.1</t>
+  </si>
+  <si>
+    <t>Address.type</t>
+  </si>
+  <si>
+    <t>Location.address.text</t>
+  </si>
+  <si>
+    <t>Text representation of the address</t>
+  </si>
+  <si>
+    <t>Specifies the entire address as it should be displayed e.g. on a postal label. This may be provided instead of or as well as the specific parts.</t>
+  </si>
+  <si>
+    <t>Can provide both a text representation and parts. Applications updating an address SHALL ensure that  when both text and parts are present,  no content is included in the text that isn't found in a part.</t>
+  </si>
+  <si>
+    <t>A renderable, unencoded form.</t>
+  </si>
+  <si>
+    <t>137 Nowhere Street, Erewhon 9132</t>
+  </si>
+  <si>
+    <t>Address.text</t>
+  </si>
+  <si>
+    <t>./formatted</t>
+  </si>
+  <si>
+    <t>Location.address.line</t>
+  </si>
+  <si>
+    <t>Street name, number, direction &amp; P.O. Box etc.</t>
+  </si>
+  <si>
+    <t>This component contains the house number, apartment number, street name, street direction,  P.O. Box number, delivery hints, and similar address information.</t>
+  </si>
+  <si>
+    <t>137 Nowhere Street</t>
+  </si>
+  <si>
+    <t>Address.line</t>
+  </si>
+  <si>
+    <t>AD.part[parttype = AL]</t>
+  </si>
+  <si>
+    <t>Location.address.city</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Municpality
+</t>
+  </si>
+  <si>
+    <t>Name of city, town etc.</t>
+  </si>
+  <si>
+    <t>The name of the city, town, suburb, village or other community or delivery center.</t>
+  </si>
+  <si>
+    <t>Erewhon</t>
+  </si>
+  <si>
+    <t>Address.city</t>
+  </si>
+  <si>
+    <t>AD.part[parttype = CTY]</t>
+  </si>
+  <si>
+    <t>Location.address.district</t>
+  </si>
+  <si>
+    <t xml:space="preserve">County
+</t>
+  </si>
+  <si>
+    <t>District name (aka county)</t>
+  </si>
+  <si>
+    <t>The name of the administrative area (county).</t>
+  </si>
+  <si>
+    <t>District is sometimes known as county, but in some regions 'county' is used in place of city (municipality), so county name should be conveyed in city instead.</t>
+  </si>
+  <si>
+    <t>Madison</t>
+  </si>
+  <si>
+    <t>Address.district</t>
+  </si>
+  <si>
+    <t>AD.part[parttype = CNT | CPA]</t>
+  </si>
+  <si>
+    <t>Location.address.state</t>
+  </si>
+  <si>
+    <t>Province
+Territory</t>
+  </si>
+  <si>
+    <t>Sub-unit of country (abbreviations ok)</t>
+  </si>
+  <si>
+    <t>Sub-unit of a country with limited sovereignty in a federally organized country. A code may be used if codes are in common use (e.g. US 2 letter state codes).</t>
+  </si>
+  <si>
+    <t>Address.state</t>
+  </si>
+  <si>
+    <t>AD.part[parttype = STA]</t>
+  </si>
+  <si>
+    <t>Location.address.postalCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zip
+</t>
+  </si>
+  <si>
+    <t>Postal code for area</t>
+  </si>
+  <si>
+    <t>A postal code designating a region defined by the postal service.</t>
+  </si>
+  <si>
+    <t>9132</t>
+  </si>
+  <si>
+    <t>Address.postalCode</t>
+  </si>
+  <si>
+    <t>AD.part[parttype = ZIP]</t>
+  </si>
+  <si>
+    <t>Location.address.country</t>
+  </si>
+  <si>
+    <t>Country (e.g. can be ISO 3166 2 or 3 letter code)</t>
+  </si>
+  <si>
+    <t>Country - a nation as commonly understood or generally accepted.</t>
+  </si>
+  <si>
+    <t>ISO 3166 3 letter codes can be used in place of a human readable country name.</t>
+  </si>
+  <si>
+    <t>Address.country</t>
+  </si>
+  <si>
+    <t>AD.part[parttype = CNT]</t>
+  </si>
+  <si>
+    <t>Location.address.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Time period when address was/is in use</t>
+  </si>
+  <si>
+    <t>Time period when address was/is in use.</t>
+  </si>
+  <si>
+    <t>Allows addresses to be placed in historical context.</t>
+  </si>
+  <si>
+    <t>&lt;valuePeriod xmlns="http://hl7.org/fhir"&gt;
+  &lt;start value="2010-03-23"/&gt;
+  &lt;end value="2010-07-01"/&gt;
+&lt;/valuePeriod&gt;</t>
+  </si>
+  <si>
+    <t>Address.period</t>
+  </si>
+  <si>
+    <t>./usablePeriod[type="IVL&lt;TS&gt;"]</t>
   </si>
   <si>
     <t>Location.physicalType</t>
@@ -1298,12 +1595,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL48"/>
+  <dimension ref="A1:AL64"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="36.84765625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="36.84765625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="13.2109375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1320,7 +1617,7 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="34.26953125" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
@@ -2534,7 +2831,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>148</v>
       </c>
@@ -2553,7 +2850,7 @@
         <v>84</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>85</v>
@@ -2746,7 +3043,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>163</v>
       </c>
@@ -2765,7 +3062,7 @@
         <v>84</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>75</v>
@@ -3828,7 +4125,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>223</v>
       </c>
@@ -3847,7 +4144,7 @@
         <v>84</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>75</v>
@@ -3938,7 +4235,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
         <v>230</v>
       </c>
@@ -3957,27 +4254,25 @@
         <v>84</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>231</v>
+        <v>195</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="N25" s="2"/>
-      <c r="O25" t="s" s="2">
-        <v>233</v>
-      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>75</v>
       </c>
@@ -4001,13 +4296,13 @@
         <v>75</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>234</v>
+        <v>75</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>235</v>
+        <v>75</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>236</v>
+        <v>75</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>75</v>
@@ -4025,7 +4320,7 @@
         <v>75</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>230</v>
+        <v>197</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -4037,32 +4332,32 @@
         <v>75</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>237</v>
+        <v>162</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>186</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>75</v>
+        <v>129</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>75</v>
@@ -4074,15 +4369,17 @@
         <v>75</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>164</v>
+        <v>130</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>195</v>
+        <v>131</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>133</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>75</v>
@@ -4119,31 +4416,31 @@
         <v>75</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>75</v>
+        <v>200</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>75</v>
+        <v>201</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>75</v>
+        <v>202</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>75</v>
+        <v>135</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>162</v>
@@ -4154,21 +4451,23 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="C27" s="2"/>
+        <v>231</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="D27" t="s" s="2">
-        <v>129</v>
+        <v>75</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>75</v>
@@ -4180,17 +4479,15 @@
         <v>75</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>130</v>
+        <v>234</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>131</v>
+        <v>235</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>133</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>75</v>
@@ -4227,16 +4524,16 @@
         <v>75</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>201</v>
+        <v>75</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>202</v>
+        <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
         <v>203</v>
@@ -4254,20 +4551,22 @@
         <v>135</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>162</v>
+        <v>75</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="C28" s="2"/>
+        <v>231</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="D28" t="s" s="2">
         <v>75</v>
       </c>
@@ -4276,32 +4575,28 @@
         <v>76</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>157</v>
+        <v>239</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>205</v>
+        <v>240</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>208</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>75</v>
       </c>
@@ -4349,7 +4644,7 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
@@ -4361,23 +4656,25 @@
         <v>75</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>210</v>
+        <v>75</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="C29" s="2"/>
+        <v>231</v>
+      </c>
+      <c r="C29" t="s" s="2">
+        <v>243</v>
+      </c>
       <c r="D29" t="s" s="2">
         <v>75</v>
       </c>
@@ -4389,29 +4686,25 @@
         <v>84</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>164</v>
+        <v>244</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>212</v>
+        <v>245</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>215</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>75</v>
       </c>
@@ -4459,22 +4752,22 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>217</v>
+        <v>75</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>75</v>
@@ -4482,12 +4775,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="C30" s="2"/>
+        <v>231</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="D30" t="s" s="2">
         <v>75</v>
       </c>
@@ -4508,18 +4803,16 @@
         <v>75</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="N30" s="2"/>
-      <c r="O30" t="s" s="2">
-        <v>246</v>
-      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>75</v>
       </c>
@@ -4567,22 +4860,22 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>242</v>
+        <v>203</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>247</v>
+        <v>75</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>75</v>
@@ -4590,10 +4883,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4610,22 +4903,26 @@
         <v>75</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>164</v>
+        <v>104</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>195</v>
+        <v>252</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>255</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>75</v>
       </c>
@@ -4637,7 +4934,7 @@
         <v>75</v>
       </c>
       <c r="T31" t="s" s="2">
-        <v>75</v>
+        <v>256</v>
       </c>
       <c r="U31" t="s" s="2">
         <v>75</v>
@@ -4649,13 +4946,13 @@
         <v>75</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>75</v>
+        <v>257</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>75</v>
+        <v>258</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>75</v>
@@ -4673,7 +4970,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>197</v>
+        <v>259</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -4685,10 +4982,10 @@
         <v>75</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>162</v>
+        <v>260</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>75</v>
@@ -4696,21 +4993,21 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>129</v>
+        <v>75</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>75</v>
@@ -4719,19 +5016,19 @@
         <v>75</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>131</v>
+        <v>262</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>199</v>
+        <v>263</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>133</v>
+        <v>264</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -4745,7 +5042,7 @@
         <v>75</v>
       </c>
       <c r="T32" t="s" s="2">
-        <v>75</v>
+        <v>265</v>
       </c>
       <c r="U32" t="s" s="2">
         <v>75</v>
@@ -4757,13 +5054,13 @@
         <v>75</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>75</v>
+        <v>266</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>75</v>
+        <v>267</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>75</v>
@@ -4781,22 +5078,22 @@
         <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>203</v>
+        <v>268</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>162</v>
+        <v>260</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>75</v>
@@ -4804,45 +5101,45 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>250</v>
+        <v>269</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>250</v>
+        <v>269</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>251</v>
+        <v>75</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J33" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>130</v>
+        <v>164</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>133</v>
+        <v>272</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>139</v>
+        <v>273</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>75</v>
@@ -4855,7 +5152,7 @@
         <v>75</v>
       </c>
       <c r="T33" t="s" s="2">
-        <v>75</v>
+        <v>274</v>
       </c>
       <c r="U33" t="s" s="2">
         <v>75</v>
@@ -4891,33 +5188,33 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>254</v>
+        <v>275</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>127</v>
+        <v>276</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>255</v>
+        <v>277</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>255</v>
+        <v>277</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4925,28 +5222,28 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>256</v>
+        <v>164</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>258</v>
+        <v>279</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4961,7 +5258,7 @@
         <v>75</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>75</v>
+        <v>280</v>
       </c>
       <c r="U34" t="s" s="2">
         <v>75</v>
@@ -4997,13 +5294,13 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>255</v>
+        <v>281</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>75</v>
@@ -5012,7 +5309,7 @@
         <v>96</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>259</v>
+        <v>282</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>75</v>
@@ -5020,18 +5317,18 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>260</v>
+        <v>283</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>260</v>
+        <v>283</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>75</v>
+        <v>284</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>84</v>
@@ -5043,16 +5340,16 @@
         <v>75</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>256</v>
+        <v>164</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>261</v>
+        <v>285</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>262</v>
+        <v>286</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5067,7 +5364,7 @@
         <v>75</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>75</v>
+        <v>287</v>
       </c>
       <c r="U35" t="s" s="2">
         <v>75</v>
@@ -5103,10 +5400,10 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>260</v>
+        <v>288</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>84</v>
@@ -5118,7 +5415,7 @@
         <v>96</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>259</v>
+        <v>289</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>75</v>
@@ -5126,14 +5423,14 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>263</v>
+        <v>290</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>263</v>
+        <v>290</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>75</v>
+        <v>291</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5149,18 +5446,20 @@
         <v>75</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>256</v>
+        <v>164</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>264</v>
+        <v>292</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>293</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>294</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>75</v>
@@ -5173,7 +5472,7 @@
         <v>75</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>75</v>
+        <v>295</v>
       </c>
       <c r="U36" t="s" s="2">
         <v>75</v>
@@ -5209,7 +5508,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>263</v>
+        <v>296</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -5224,7 +5523,7 @@
         <v>96</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>259</v>
+        <v>297</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>75</v>
@@ -5232,14 +5531,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>266</v>
+        <v>298</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>266</v>
+        <v>298</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>75</v>
+        <v>299</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -5258,20 +5557,16 @@
         <v>85</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>267</v>
+        <v>164</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>268</v>
+        <v>300</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>271</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>75</v>
       </c>
@@ -5319,7 +5614,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>266</v>
+        <v>302</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5334,7 +5629,7 @@
         <v>96</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>272</v>
+        <v>303</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>75</v>
@@ -5342,14 +5637,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>273</v>
+        <v>304</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>273</v>
+        <v>304</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>75</v>
+        <v>305</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -5365,21 +5660,19 @@
         <v>75</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>274</v>
+        <v>164</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>275</v>
+        <v>306</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>276</v>
+        <v>307</v>
       </c>
       <c r="N38" s="2"/>
-      <c r="O38" t="s" s="2">
-        <v>277</v>
-      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>75</v>
       </c>
@@ -5391,7 +5684,7 @@
         <v>75</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>75</v>
+        <v>308</v>
       </c>
       <c r="U38" t="s" s="2">
         <v>75</v>
@@ -5427,7 +5720,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>273</v>
+        <v>309</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -5442,7 +5735,7 @@
         <v>96</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>278</v>
+        <v>310</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>75</v>
@@ -5450,10 +5743,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>279</v>
+        <v>311</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>279</v>
+        <v>311</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5464,7 +5757,7 @@
         <v>76</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>75</v>
@@ -5473,19 +5766,19 @@
         <v>75</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>243</v>
+        <v>164</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>280</v>
+        <v>312</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>281</v>
+        <v>313</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>282</v>
+        <v>314</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5535,13 +5828,13 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>279</v>
+        <v>315</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>75</v>
@@ -5550,7 +5843,7 @@
         <v>96</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>283</v>
+        <v>316</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>75</v>
@@ -5558,10 +5851,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>284</v>
+        <v>317</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>284</v>
+        <v>317</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5581,19 +5874,21 @@
         <v>75</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>164</v>
+        <v>318</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>195</v>
+        <v>319</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>196</v>
+        <v>320</v>
       </c>
       <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+      <c r="O40" t="s" s="2">
+        <v>321</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>75</v>
       </c>
@@ -5605,7 +5900,7 @@
         <v>75</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>75</v>
+        <v>322</v>
       </c>
       <c r="U40" t="s" s="2">
         <v>75</v>
@@ -5641,7 +5936,7 @@
         <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>197</v>
+        <v>323</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -5653,55 +5948,55 @@
         <v>75</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>162</v>
+        <v>324</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
-        <v>285</v>
+        <v>325</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>285</v>
+        <v>325</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>129</v>
+        <v>75</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>130</v>
+        <v>188</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>131</v>
+        <v>326</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>327</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" t="s" s="2">
+        <v>328</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>75</v>
       </c>
@@ -5725,13 +6020,13 @@
         <v>75</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>75</v>
+        <v>329</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>75</v>
+        <v>330</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>75</v>
+        <v>331</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>75</v>
@@ -5749,69 +6044,65 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>203</v>
+        <v>325</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>162</v>
+        <v>332</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>75</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>286</v>
+        <v>333</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>286</v>
+        <v>333</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>251</v>
+        <v>75</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>130</v>
+        <v>164</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>75</v>
       </c>
@@ -5859,22 +6150,22 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>254</v>
+        <v>197</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>135</v>
+        <v>75</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>127</v>
+        <v>162</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>75</v>
@@ -5882,14 +6173,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>287</v>
+        <v>334</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>287</v>
+        <v>334</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>75</v>
+        <v>129</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -5908,15 +6199,17 @@
         <v>75</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>288</v>
+        <v>131</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>133</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>75</v>
@@ -5941,31 +6234,31 @@
         <v>75</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>290</v>
+        <v>75</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>291</v>
+        <v>75</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>75</v>
+        <v>200</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>75</v>
+        <v>201</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>75</v>
+        <v>202</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>287</v>
+        <v>203</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -5977,21 +6270,21 @@
         <v>75</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>283</v>
+        <v>162</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
-        <v>292</v>
+        <v>335</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>292</v>
+        <v>335</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6002,28 +6295,32 @@
         <v>76</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>293</v>
+        <v>157</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>294</v>
+        <v>205</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>208</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>75</v>
       </c>
@@ -6071,13 +6368,13 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>292</v>
+        <v>209</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>75</v>
@@ -6086,18 +6383,18 @@
         <v>96</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>283</v>
+        <v>210</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
-        <v>296</v>
+        <v>336</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>296</v>
+        <v>336</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6111,25 +6408,29 @@
         <v>84</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>297</v>
+        <v>164</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>298</v>
+        <v>212</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+        <v>213</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>215</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>75</v>
       </c>
@@ -6177,7 +6478,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>296</v>
+        <v>216</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -6192,18 +6493,18 @@
         <v>96</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>283</v>
+        <v>217</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
-        <v>300</v>
+        <v>337</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>300</v>
+        <v>337</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6217,7 +6518,7 @@
         <v>84</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>75</v>
@@ -6226,16 +6527,18 @@
         <v>75</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>297</v>
+        <v>338</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>301</v>
+        <v>339</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>302</v>
+        <v>340</v>
       </c>
       <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+      <c r="O46" t="s" s="2">
+        <v>341</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>75</v>
       </c>
@@ -6283,7 +6586,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>300</v>
+        <v>337</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -6298,7 +6601,7 @@
         <v>96</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>283</v>
+        <v>342</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>75</v>
@@ -6306,10 +6609,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>303</v>
+        <v>343</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>303</v>
+        <v>343</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6335,10 +6638,10 @@
         <v>164</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>304</v>
+        <v>195</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>305</v>
+        <v>196</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6389,7 +6692,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>303</v>
+        <v>197</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -6401,7 +6704,7 @@
         <v>75</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>162</v>
@@ -6412,14 +6715,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>306</v>
+        <v>344</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>306</v>
+        <v>344</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>75</v>
+        <v>129</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -6438,18 +6741,18 @@
         <v>75</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>307</v>
+        <v>130</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>308</v>
+        <v>131</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" t="s" s="2">
-        <v>310</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>75</v>
       </c>
@@ -6497,7 +6800,7 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>306</v>
+        <v>203</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -6509,7 +6812,7 @@
         <v>75</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>162</v>
@@ -6518,8 +6821,1724 @@
         <v>75</v>
       </c>
     </row>
+    <row r="49" hidden="true">
+      <c r="A49" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="P49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
+      <c r="P50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
+      <c r="P51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="52" hidden="true">
+      <c r="A52" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
+      <c r="P52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="P53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="54" hidden="true">
+      <c r="A54" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="P54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="55" hidden="true">
+      <c r="A55" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="O55" s="2"/>
+      <c r="P55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="56" hidden="true">
+      <c r="A56" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
+      <c r="P56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="57" hidden="true">
+      <c r="A57" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="O57" s="2"/>
+      <c r="P57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="P58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="59" hidden="true">
+      <c r="A59" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
+      <c r="P59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="61" hidden="true">
+      <c r="A61" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="62" hidden="true">
+      <c r="A62" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="P64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AL48">
+  <autoFilter ref="A1:AL64">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -6529,7 +8548,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI47">
+  <conditionalFormatting sqref="A2:AI63">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/dev/StructureDefinition-ph-core-location.xlsx
+++ b/dev/StructureDefinition-ph-core-location.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T03:51:01+00:00</t>
+    <t>2026-05-26T04:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-location.xlsx
+++ b/dev/StructureDefinition-ph-core-location.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T04:00:40+00:00</t>
+    <t>2026-05-26T04:36:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
